--- a/Design/Excel/ET/Datas/Game/Sound.xlsx
+++ b/Design/Excel/ET/Datas/Game/Sound.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" activeTab="2"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="UISound" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -88,57 +88,12 @@
     <t>音量（0~1）</t>
   </si>
   <si>
-    <t>Select</t>
-  </si>
-  <si>
-    <t>选择音效</t>
-  </si>
-  <si>
-    <t>select</t>
-  </si>
-  <si>
-    <t>Click</t>
-  </si>
-  <si>
-    <t>点击音效</t>
-  </si>
-  <si>
-    <t>click</t>
-  </si>
-  <si>
     <t>string#path=normal;Music/*.mp3</t>
   </si>
   <si>
     <t>音乐编号</t>
   </si>
   <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>菜单音乐</t>
-  </si>
-  <si>
-    <t>music_menu</t>
-  </si>
-  <si>
-    <t>Background</t>
-  </si>
-  <si>
-    <t>战斗音乐</t>
-  </si>
-  <si>
-    <t>music_background</t>
-  </si>
-  <si>
-    <t>About</t>
-  </si>
-  <si>
-    <t>关于音乐</t>
-  </si>
-  <si>
-    <t>music_about</t>
-  </si>
-  <si>
     <t>SoundGroupName</t>
   </si>
   <si>
@@ -173,54 +128,6 @@
   </si>
   <si>
     <t>声音最大距离</t>
-  </si>
-  <si>
-    <t>WeaponPlayer</t>
-  </si>
-  <si>
-    <t>玩家子弹</t>
-  </si>
-  <si>
-    <t>weapon_player</t>
-  </si>
-  <si>
-    <t>Sound.Default</t>
-  </si>
-  <si>
-    <t>WeaponEnemy</t>
-  </si>
-  <si>
-    <t>敌人子弹</t>
-  </si>
-  <si>
-    <t>weapon_enemy</t>
-  </si>
-  <si>
-    <t>ExplosionPlayer</t>
-  </si>
-  <si>
-    <t>玩家爆炸</t>
-  </si>
-  <si>
-    <t>explosion_player</t>
-  </si>
-  <si>
-    <t>ExplosionEnemy</t>
-  </si>
-  <si>
-    <t>敌人爆炸</t>
-  </si>
-  <si>
-    <t>explosion_enemy</t>
-  </si>
-  <si>
-    <t>ExplosionAsteroid</t>
-  </si>
-  <si>
-    <t>小行星爆炸</t>
-  </si>
-  <si>
-    <t>explosion_asteroid</t>
   </si>
 </sst>
 </file>
@@ -1275,44 +1182,20 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="B4" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="3">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1324,8 +1207,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="11" style="2"/>
     <col min="3" max="3" width="14.3727272727273" style="2" customWidth="1"/>
@@ -1369,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
@@ -1380,7 +1263,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -1393,57 +1276,6 @@
       </c>
       <c r="F3" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1455,8 +1287,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="2" width="11" style="1"/>
     <col min="3" max="3" width="21.8727272727273" style="1" customWidth="1"/>
@@ -1487,22 +1319,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1513,22 +1345,22 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>11</v>
@@ -1557,182 +1389,22 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="1">
-        <v>20000</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
